--- a/Digital Chess Clock/Grading/2 stage/3-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-04_3-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
+++ b/Digital Chess Clock/Grading/2 stage/3-examples/Digital-Chess-Clock_Grading_2-stage_2026-03-04_3-examples_HumanGrading_Claude4.5SonnetGeneration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/Evaluations 2/Digital Chess Clock/Grading/2 stage/2026-03-04/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marc-antoinenadeau/Desktop/B.Eng Software Engineering /7th Semester/Capstone/Code/Evaluations/Digital Chess Clock/Grading/2 stage/3-examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E6886C-4106-E54D-98CD-032CC4777221}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF124CF7-AA7A-C049-B3D2-60CAFE9D4FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-160" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chess Clock" sheetId="1" r:id="rId1"/>
@@ -763,17 +763,17 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -906,34 +906,28 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -959,8 +953,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="6"/>
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1031,8 +1025,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1184,24 +1178,24 @@
       <tableStyleElement type="secondRowStripe" dxfId="12"/>
     </tableStyle>
     <tableStyle name="Metrics-style 2" pivot="0" count="3" xr9:uid="{9DCFDD21-0610-724A-8E4B-C10801BBFF7E}">
+      <tableStyleElement type="headerRow" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="secondRowStripe" dxfId="9"/>
+    </tableStyle>
+    <tableStyle name="Metrics-style 3" pivot="0" count="3" xr9:uid="{02D054DC-BA84-9840-8843-92093BC9473B}">
       <tableStyleElement type="headerRow" dxfId="8"/>
       <tableStyleElement type="firstRowStripe" dxfId="7"/>
       <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
-    <tableStyle name="Metrics-style 3" pivot="0" count="3" xr9:uid="{02D054DC-BA84-9840-8843-92093BC9473B}">
+    <tableStyle name="Metrics-style 4" pivot="0" count="3" xr9:uid="{5ECBD757-D05A-BD4A-9992-DD217BBCB878}">
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="firstRowStripe" dxfId="4"/>
       <tableStyleElement type="secondRowStripe" dxfId="3"/>
     </tableStyle>
-    <tableStyle name="Metrics-style 4" pivot="0" count="3" xr9:uid="{5ECBD757-D05A-BD4A-9992-DD217BBCB878}">
+    <tableStyle name="Weighted Cohens Kappa-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
       <tableStyleElement type="headerRow" dxfId="2"/>
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="secondRowStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="Weighted Cohens Kappa-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
-      <tableStyleElement type="headerRow" dxfId="11"/>
-      <tableStyleElement type="firstRowStripe" dxfId="10"/>
-      <tableStyleElement type="secondRowStripe" dxfId="9"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1303,7 +1297,9 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Type"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Element"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Rater 1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Rater 2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Rater 2">
+      <calculatedColumnFormula>'Chess Clock Grader #2'!C2</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="Weighted Cohens Kappa-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -16410,7 +16406,7 @@
       <c r="F1" s="59"/>
       <c r="G1" s="59"/>
       <c r="H1" s="59"/>
-      <c r="J1" s="64" t="s">
+      <c r="J1" s="55" t="s">
         <v>61</v>
       </c>
     </row>
@@ -16439,7 +16435,7 @@
       <c r="H2" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="65" t="s">
+      <c r="J2" s="56" t="s">
         <v>114</v>
       </c>
     </row>
@@ -16509,7 +16505,7 @@
         <f t="shared" si="2"/>
         <v>0.91666666666666663</v>
       </c>
-      <c r="J4" s="64" t="s">
+      <c r="J4" s="55" t="s">
         <v>110</v>
       </c>
     </row>
@@ -16545,7 +16541,7 @@
         <f t="shared" si="2"/>
         <v>0.88888888888888895</v>
       </c>
-      <c r="J5" s="66">
+      <c r="J5" s="57">
         <v>1</v>
       </c>
     </row>
@@ -16615,7 +16611,7 @@
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="J7" s="64" t="s">
+      <c r="J7" s="55" t="s">
         <v>111</v>
       </c>
     </row>
@@ -16651,7 +16647,7 @@
         <f t="shared" si="2"/>
         <v>Not Available</v>
       </c>
-      <c r="J8" s="66">
+      <c r="J8" s="57">
         <v>4</v>
       </c>
     </row>
@@ -16721,12 +16717,12 @@
         <f t="shared" si="2"/>
         <v>0.93641618497109824</v>
       </c>
-      <c r="J10" s="64" t="s">
+      <c r="J10" s="55" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="J11" s="65" t="s">
+      <c r="J11" s="56" t="s">
         <v>113</v>
       </c>
     </row>
@@ -18062,17 +18058,17 @@
         <v>73</v>
       </c>
       <c r="E1" s="26"/>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="L1" s="62" t="s">
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="L1" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
+      <c r="M1" s="61"/>
+      <c r="N1" s="61"/>
     </row>
     <row r="2" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -18342,17 +18338,17 @@
         <v>1</v>
       </c>
       <c r="E8" s="26"/>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
-      <c r="L8" s="62" t="s">
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
+      <c r="L8" s="60" t="s">
         <v>91</v>
       </c>
-      <c r="M8" s="63"/>
-      <c r="N8" s="63"/>
+      <c r="M8" s="61"/>
+      <c r="N8" s="61"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -18619,17 +18615,17 @@
         <v>1</v>
       </c>
       <c r="E15" s="26"/>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="L15" s="62" t="s">
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
+      <c r="L15" s="60" t="s">
         <v>93</v>
       </c>
-      <c r="M15" s="63"/>
-      <c r="N15" s="63"/>
+      <c r="M15" s="61"/>
+      <c r="N15" s="61"/>
     </row>
     <row r="16" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -18896,17 +18892,17 @@
         <v>1</v>
       </c>
       <c r="E22" s="26"/>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-      <c r="L22" s="62" t="s">
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="L22" s="60" t="s">
         <v>95</v>
       </c>
-      <c r="M22" s="63"/>
-      <c r="N22" s="63"/>
+      <c r="M22" s="61"/>
+      <c r="N22" s="61"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -19173,17 +19169,17 @@
         <v>1</v>
       </c>
       <c r="E29" s="26"/>
-      <c r="F29" s="60" t="s">
+      <c r="F29" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
-      <c r="L29" s="62" t="s">
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
+      <c r="L29" s="60" t="s">
         <v>97</v>
       </c>
-      <c r="M29" s="63"/>
-      <c r="N29" s="63"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
     </row>
     <row r="30" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -19450,17 +19446,17 @@
         <v>0</v>
       </c>
       <c r="E36" s="26"/>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
-      <c r="L36" s="62" t="s">
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
+      <c r="L36" s="60" t="s">
         <v>99</v>
       </c>
-      <c r="M36" s="63"/>
-      <c r="N36" s="63"/>
+      <c r="M36" s="61"/>
+      <c r="N36" s="61"/>
     </row>
     <row r="37" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -19727,17 +19723,17 @@
         <v>1</v>
       </c>
       <c r="E43" s="26"/>
-      <c r="F43" s="60" t="s">
+      <c r="F43" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
-      <c r="L43" s="62" t="s">
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
+      <c r="L43" s="60" t="s">
         <v>101</v>
       </c>
-      <c r="M43" s="63"/>
-      <c r="N43" s="63"/>
+      <c r="M43" s="61"/>
+      <c r="N43" s="61"/>
     </row>
     <row r="44" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -20004,17 +20000,17 @@
         <v>0</v>
       </c>
       <c r="E50" s="26"/>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61"/>
-      <c r="L50" s="62" t="s">
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
+      <c r="L50" s="60" t="s">
         <v>103</v>
       </c>
-      <c r="M50" s="63"/>
-      <c r="N50" s="63"/>
+      <c r="M50" s="61"/>
+      <c r="N50" s="61"/>
     </row>
     <row r="51" spans="1:14" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -21266,6 +21262,12 @@
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L1:N1"/>
+    <mergeCell ref="F8:I8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="F15:I15"/>
+    <mergeCell ref="L15:N15"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="L50:N50"/>
@@ -21276,12 +21278,6 @@
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="F43:I43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="F8:I8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="F15:I15"/>
-    <mergeCell ref="L15:N15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -21330,18 +21326,18 @@
         <v>73</v>
       </c>
       <c r="E1" s="26"/>
-      <c r="F1" s="60" t="s">
+      <c r="F1" s="62" t="s">
         <v>74</v>
       </c>
-      <c r="G1" s="61"/>
-      <c r="H1" s="61"/>
-      <c r="I1" s="61"/>
-      <c r="L1" s="60" t="s">
+      <c r="G1" s="63"/>
+      <c r="H1" s="63"/>
+      <c r="I1" s="63"/>
+      <c r="L1" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
+      <c r="M1" s="63"/>
+      <c r="N1" s="63"/>
+      <c r="O1" s="63"/>
     </row>
     <row r="2" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="str">
@@ -21357,7 +21353,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="4">
-        <f>'Chess Clock Grader #1'!C2</f>
+        <f>'Chess Clock Grader #2'!C2</f>
         <v>1</v>
       </c>
       <c r="E2" s="26"/>
@@ -21426,7 +21422,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <f>'Chess Clock Grader #1'!C3</f>
+        <f>'Chess Clock Grader #2'!C3</f>
         <v>1</v>
       </c>
       <c r="E3" s="26"/>
@@ -21435,7 +21431,7 @@
       </c>
       <c r="G3" s="39">
         <f>COUNTIFS($C$2:$C$90, $F3, $D$2:$D$90, G$2)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="40">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, H$2)</f>
@@ -21443,7 +21439,7 @@
       </c>
       <c r="I3" s="41">
         <f>COUNTIFS($C$2:$C$46, $F3, $D$2:$D$46, I$2)+MAX(D47-C47,0)+MAX(D48-C48,0)+MAX(D49-C49,0)+MAX(D50-C50,0)+MAX(D51-C51,0)+MAX(D52-C52,0)+MAX(D53-C53,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" s="11">
         <f t="shared" ref="J3:J5" si="0">SUM(G3:I3)</f>
@@ -21471,15 +21467,15 @@
       </c>
       <c r="R3" s="39">
         <f t="shared" ref="R3:T3" si="2">($J3/$J$6) * (G$6/$J$6)</f>
-        <v>1.8121301775147928E-2</v>
+        <v>2.3298816568047335E-2</v>
       </c>
       <c r="S3" s="40">
         <f t="shared" si="2"/>
-        <v>1.8121301775147928E-2</v>
+        <v>5.1775147928994087E-3</v>
       </c>
       <c r="T3" s="41">
         <f t="shared" si="2"/>
-        <v>9.8372781065088746E-2</v>
+        <v>0.10613905325443786</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" s="42" t="s">
@@ -21487,7 +21483,7 @@
       </c>
       <c r="W3" s="39">
         <f>SUMPRODUCT(G3:I5, M3:O5) /$J$6</f>
-        <v>0</v>
+        <v>0.16346153846153846</v>
       </c>
       <c r="X3" s="41" t="s">
         <v>106</v>
@@ -21507,7 +21503,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="4">
-        <f>'Chess Clock Grader #1'!C4</f>
+        <f>'Chess Clock Grader #2'!C4</f>
         <v>1</v>
       </c>
       <c r="E4" s="26"/>
@@ -21520,11 +21516,11 @@
       </c>
       <c r="H4" s="11">
         <f t="shared" si="3"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I4" s="44">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J4" s="11">
         <f t="shared" si="0"/>
@@ -21552,15 +21548,15 @@
       </c>
       <c r="R4" s="43">
         <f t="shared" ref="R4:T4" si="5">($J4/$J$6) * (G$6/$J$6)</f>
-        <v>1.8121301775147928E-2</v>
+        <v>2.3298816568047335E-2</v>
       </c>
       <c r="S4" s="11">
         <f t="shared" si="5"/>
-        <v>1.8121301775147928E-2</v>
+        <v>5.1775147928994087E-3</v>
       </c>
       <c r="T4" s="44">
         <f t="shared" si="5"/>
-        <v>9.8372781065088746E-2</v>
+        <v>0.10613905325443786</v>
       </c>
       <c r="U4" s="11"/>
       <c r="V4" s="42" t="s">
@@ -21568,7 +21564,7 @@
       </c>
       <c r="W4" s="43">
         <f>SUMPRODUCT(R3:T5, M3:O5)</f>
-        <v>0.31323964497041418</v>
+        <v>0.31397928994082835</v>
       </c>
       <c r="X4" s="44" t="s">
         <v>108</v>
@@ -21588,7 +21584,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="4">
-        <f>'Chess Clock Grader #1'!C5</f>
+        <f>'Chess Clock Grader #2'!C5</f>
         <v>1</v>
       </c>
       <c r="E5" s="26"/>
@@ -21597,15 +21593,15 @@
       </c>
       <c r="G5" s="45">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, G$2)+MAX(C47-D47,0)+MAX(C48-D48,0)+MAX(C49-D49,0)+MAX(C50-D50,0)+MAX(C51-D51,0)+MAX(C52-D52,0)+MAX(C53-D53,0)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H5" s="46">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, H$2)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" s="47">
         <f>COUNTIFS($C$2:$C$46, $F5, $D$2:$D$46, I$2)+ SUM(MIN(C47,D47), MIN(C48,D48), MIN(C49,D49), MIN(C50,D50), MIN(C51,D51), MIN(C52,D52), MIN(C53,D53))</f>
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="J5" s="11">
         <f t="shared" si="0"/>
@@ -21633,15 +21629,15 @@
       </c>
       <c r="R5" s="45">
         <f t="shared" ref="R5:T5" si="7">($J5/$J$6) * (G$6/$J$6)</f>
-        <v>9.8372781065088746E-2</v>
+        <v>0.12647928994082838</v>
       </c>
       <c r="S5" s="46">
         <f t="shared" si="7"/>
-        <v>9.8372781065088746E-2</v>
+        <v>2.8106508875739646E-2</v>
       </c>
       <c r="T5" s="47">
         <f t="shared" si="7"/>
-        <v>0.53402366863905315</v>
+        <v>0.57618343195266264</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="42" t="s">
@@ -21649,7 +21645,7 @@
       </c>
       <c r="W5" s="45">
         <f>1-W3/W4</f>
-        <v>1</v>
+        <v>0.47938751472320373</v>
       </c>
       <c r="X5" s="47" t="s">
         <v>109</v>
@@ -21669,7 +21665,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="4">
-        <f>'Chess Clock Grader #1'!C6</f>
+        <f>'Chess Clock Grader #2'!C6</f>
         <v>1</v>
       </c>
       <c r="E6" s="26"/>
@@ -21678,15 +21674,15 @@
       </c>
       <c r="G6" s="11">
         <f t="shared" ref="G6:I6" si="8">SUM(G3:G5)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H6" s="11">
         <f t="shared" si="8"/>
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I6" s="11">
         <f t="shared" si="8"/>
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J6" s="11">
         <f>SUM(G3:I5)</f>
@@ -21718,7 +21714,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="4">
-        <f>'Chess Clock Grader #1'!C7</f>
+        <f>'Chess Clock Grader #2'!C7</f>
         <v>1</v>
       </c>
       <c r="E7" s="26"/>
@@ -21740,16 +21736,16 @@
         <v>1</v>
       </c>
       <c r="D8" s="4">
-        <f>'Chess Clock Grader #1'!C8</f>
+        <f>'Chess Clock Grader #2'!C8</f>
         <v>1</v>
       </c>
       <c r="E8" s="26"/>
-      <c r="F8" s="60" t="s">
+      <c r="F8" s="62" t="s">
         <v>90</v>
       </c>
-      <c r="G8" s="61"/>
-      <c r="H8" s="61"/>
-      <c r="I8" s="61"/>
+      <c r="G8" s="63"/>
+      <c r="H8" s="63"/>
+      <c r="I8" s="63"/>
     </row>
     <row r="9" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="str">
@@ -21765,7 +21761,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="4">
-        <f>'Chess Clock Grader #1'!C9</f>
+        <f>'Chess Clock Grader #2'!C9</f>
         <v>1</v>
       </c>
       <c r="E9" s="26"/>
@@ -21834,7 +21830,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="4">
-        <f>'Chess Clock Grader #1'!C10</f>
+        <f>'Chess Clock Grader #2'!C10</f>
         <v>1</v>
       </c>
       <c r="E10" s="26"/>
@@ -21883,11 +21879,11 @@
       </c>
       <c r="S10" s="40">
         <f t="shared" si="12"/>
-        <v>2.0408163265306121E-2</v>
+        <v>0</v>
       </c>
       <c r="T10" s="41">
         <f t="shared" si="12"/>
-        <v>4.5918367346938778E-2</v>
+        <v>6.6326530612244902E-2</v>
       </c>
       <c r="U10" s="11"/>
       <c r="V10" s="42" t="s">
@@ -21895,7 +21891,7 @@
       </c>
       <c r="W10" s="39">
         <f>SUMPRODUCT(G10:I12, M10:O12) /$J$13</f>
-        <v>0</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="X10" s="41" t="s">
         <v>106</v>
@@ -21915,7 +21911,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="4">
-        <f>'Chess Clock Grader #1'!C11</f>
+        <f>'Chess Clock Grader #2'!C11</f>
         <v>1</v>
       </c>
       <c r="E11" s="26"/>
@@ -21928,11 +21924,11 @@
       </c>
       <c r="H11" s="11">
         <f t="shared" si="13"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" s="44">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J11" s="11">
         <f t="shared" si="10"/>
@@ -21964,11 +21960,11 @@
       </c>
       <c r="S11" s="11">
         <f t="shared" si="15"/>
-        <v>8.1632653061224483E-2</v>
+        <v>0</v>
       </c>
       <c r="T11" s="44">
         <f t="shared" si="15"/>
-        <v>0.18367346938775511</v>
+        <v>0.26530612244897961</v>
       </c>
       <c r="U11" s="11"/>
       <c r="V11" s="42" t="s">
@@ -21976,7 +21972,7 @@
       </c>
       <c r="W11" s="43">
         <f>SUMPRODUCT(R10:T12, M10:O12)</f>
-        <v>0.29591836734693877</v>
+        <v>0.25510204081632654</v>
       </c>
       <c r="X11" s="44" t="s">
         <v>108</v>
@@ -21996,8 +21992,8 @@
         <v>1</v>
       </c>
       <c r="D12" s="4">
-        <f>'Chess Clock Grader #1'!C12</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C12</f>
+        <v>0.5</v>
       </c>
       <c r="E12" s="26"/>
       <c r="F12" s="38">
@@ -22045,11 +22041,11 @@
       </c>
       <c r="S12" s="46">
         <f t="shared" si="17"/>
-        <v>0.18367346938775511</v>
+        <v>0</v>
       </c>
       <c r="T12" s="47">
         <f t="shared" si="17"/>
-        <v>0.41326530612244905</v>
+        <v>0.59693877551020413</v>
       </c>
       <c r="U12" s="11"/>
       <c r="V12" s="42" t="s">
@@ -22057,7 +22053,7 @@
       </c>
       <c r="W12" s="45">
         <f>1-W10/W11</f>
-        <v>1</v>
+        <v>0.44000000000000006</v>
       </c>
       <c r="X12" s="47" t="s">
         <v>109</v>
@@ -22077,8 +22073,8 @@
         <v>1</v>
       </c>
       <c r="D13" s="4">
-        <f>'Chess Clock Grader #1'!C13</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C13</f>
+        <v>0.5</v>
       </c>
       <c r="E13" s="26"/>
       <c r="F13" s="48" t="s">
@@ -22090,11 +22086,11 @@
       </c>
       <c r="H13" s="11">
         <f t="shared" si="18"/>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" s="11">
         <f t="shared" si="18"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J13" s="11">
         <f>SUM(G10:I12)</f>
@@ -22115,7 +22111,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="4">
-        <f>'Chess Clock Grader #1'!C14</f>
+        <f>'Chess Clock Grader #2'!C14</f>
         <v>1</v>
       </c>
       <c r="E14" s="26"/>
@@ -22134,16 +22130,16 @@
         <v>1</v>
       </c>
       <c r="D15" s="4">
-        <f>'Chess Clock Grader #1'!C15</f>
+        <f>'Chess Clock Grader #2'!C15</f>
         <v>1</v>
       </c>
       <c r="E15" s="26"/>
-      <c r="F15" s="60" t="s">
+      <c r="F15" s="62" t="s">
         <v>92</v>
       </c>
-      <c r="G15" s="61"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
+      <c r="G15" s="63"/>
+      <c r="H15" s="63"/>
+      <c r="I15" s="63"/>
     </row>
     <row r="16" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="str">
@@ -22159,8 +22155,8 @@
         <v>0.5</v>
       </c>
       <c r="D16" s="4">
-        <f>'Chess Clock Grader #1'!C16</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C16</f>
+        <v>1</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="11" t="s">
@@ -22228,7 +22224,7 @@
         <v>1</v>
       </c>
       <c r="D17" s="4">
-        <f>'Chess Clock Grader #1'!C17</f>
+        <f>'Chess Clock Grader #2'!C17</f>
         <v>1</v>
       </c>
       <c r="E17" s="26"/>
@@ -22237,7 +22233,7 @@
       </c>
       <c r="G17" s="39">
         <f t="shared" ref="G17:H17" si="19">COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F17,$D$2:$D$90,G$16)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H17" s="40">
         <f t="shared" si="19"/>
@@ -22245,7 +22241,7 @@
       </c>
       <c r="I17" s="41">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F17,$D$2:$D$46,I$16) + MAX(D48-C48,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" ref="J17:J19" si="20">SUM(G17:I17)</f>
@@ -22277,11 +22273,11 @@
       </c>
       <c r="S17" s="40">
         <f t="shared" si="22"/>
-        <v>8.8888888888888889E-3</v>
+        <v>0</v>
       </c>
       <c r="T17" s="41">
         <f t="shared" si="22"/>
-        <v>5.3333333333333337E-2</v>
+        <v>6.222222222222222E-2</v>
       </c>
       <c r="U17" s="11"/>
       <c r="V17" s="42" t="s">
@@ -22289,7 +22285,7 @@
       </c>
       <c r="W17" s="39">
         <f>SUMPRODUCT(G17:I19, M17:O19) /$J$20</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="X17" s="41" t="s">
         <v>106</v>
@@ -22309,8 +22305,8 @@
         <v>0.5</v>
       </c>
       <c r="D18" s="4">
-        <f>'Chess Clock Grader #1'!C18</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C18</f>
+        <v>1</v>
       </c>
       <c r="E18" s="26"/>
       <c r="F18" s="38">
@@ -22322,11 +22318,11 @@
       </c>
       <c r="H18" s="11">
         <f t="shared" si="23"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I18" s="44">
         <f t="shared" si="23"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18" s="11">
         <f t="shared" si="20"/>
@@ -22358,11 +22354,11 @@
       </c>
       <c r="S18" s="11">
         <f t="shared" si="25"/>
-        <v>1.7777777777777778E-2</v>
+        <v>0</v>
       </c>
       <c r="T18" s="44">
         <f t="shared" si="25"/>
-        <v>0.10666666666666667</v>
+        <v>0.12444444444444444</v>
       </c>
       <c r="U18" s="11"/>
       <c r="V18" s="42" t="s">
@@ -22370,7 +22366,7 @@
       </c>
       <c r="W18" s="43">
         <f>SUMPRODUCT(R17:T19, M17:O19)</f>
-        <v>0.22222222222222224</v>
+        <v>0.18222222222222223</v>
       </c>
       <c r="X18" s="44" t="s">
         <v>108</v>
@@ -22390,8 +22386,8 @@
         <v>0.5</v>
       </c>
       <c r="D19" s="4">
-        <f>'Chess Clock Grader #1'!C19</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C19</f>
+        <v>1</v>
       </c>
       <c r="E19" s="26"/>
       <c r="F19" s="38">
@@ -22399,7 +22395,7 @@
       </c>
       <c r="G19" s="45">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,G$16)+MAX(C48-D48,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" s="46">
         <f>COUNTIFS($A$2:$A$90,$F$16,$C$2:$C$90,$F19,$D$2:$D$90,H$16)</f>
@@ -22407,7 +22403,7 @@
       </c>
       <c r="I19" s="47">
         <f>COUNTIFS($A$2:$A$46,$F$16,$C$2:$C$46,$F19,$D$2:$D$46,I$16) + MIN(C48,D48)</f>
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J19" s="11">
         <f t="shared" si="20"/>
@@ -22439,11 +22435,11 @@
       </c>
       <c r="S19" s="46">
         <f t="shared" si="27"/>
-        <v>0.10666666666666667</v>
+        <v>0</v>
       </c>
       <c r="T19" s="47">
         <f t="shared" si="27"/>
-        <v>0.64000000000000012</v>
+        <v>0.7466666666666667</v>
       </c>
       <c r="U19" s="11"/>
       <c r="V19" s="42" t="s">
@@ -22451,7 +22447,7 @@
       </c>
       <c r="W19" s="45">
         <f>1-W17/W18</f>
-        <v>1</v>
+        <v>-9.7560975609756184E-2</v>
       </c>
       <c r="X19" s="47" t="s">
         <v>109</v>
@@ -22471,8 +22467,8 @@
         <v>0</v>
       </c>
       <c r="D20" s="4">
-        <f>'Chess Clock Grader #1'!C20</f>
-        <v>0</v>
+        <f>'Chess Clock Grader #2'!C20</f>
+        <v>1</v>
       </c>
       <c r="E20" s="26"/>
       <c r="F20" s="48" t="s">
@@ -22484,11 +22480,11 @@
       </c>
       <c r="H20" s="11">
         <f t="shared" si="28"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" s="11">
         <f t="shared" si="28"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J20" s="11">
         <f>SUM(G17:I19)</f>
@@ -22509,8 +22505,8 @@
         <v>0.5</v>
       </c>
       <c r="D21" s="4">
-        <f>'Chess Clock Grader #1'!C21</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C21</f>
+        <v>1</v>
       </c>
       <c r="E21" s="26"/>
     </row>
@@ -22528,16 +22524,16 @@
         <v>0.5</v>
       </c>
       <c r="D22" s="4">
-        <f>'Chess Clock Grader #1'!C22</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C22</f>
+        <v>1</v>
       </c>
       <c r="E22" s="26"/>
-      <c r="F22" s="60" t="s">
+      <c r="F22" s="62" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
     </row>
     <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="str">
@@ -22553,7 +22549,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="4">
-        <f>'Chess Clock Grader #1'!C23</f>
+        <f>'Chess Clock Grader #2'!C23</f>
         <v>1</v>
       </c>
       <c r="E23" s="26"/>
@@ -22622,7 +22618,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="4">
-        <f>'Chess Clock Grader #1'!C24</f>
+        <f>'Chess Clock Grader #2'!C24</f>
         <v>1</v>
       </c>
       <c r="E24" s="26"/>
@@ -22703,7 +22699,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="4">
-        <f>'Chess Clock Grader #1'!C25</f>
+        <f>'Chess Clock Grader #2'!C25</f>
         <v>1</v>
       </c>
       <c r="E25" s="26"/>
@@ -22784,7 +22780,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="4">
-        <f>'Chess Clock Grader #1'!C26</f>
+        <f>'Chess Clock Grader #2'!C26</f>
         <v>1</v>
       </c>
       <c r="E26" s="26"/>
@@ -22865,8 +22861,8 @@
         <v>0.5</v>
       </c>
       <c r="D27" s="4">
-        <f>'Chess Clock Grader #1'!C27</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C27</f>
+        <v>1</v>
       </c>
       <c r="E27" s="26"/>
       <c r="F27" s="48" t="s">
@@ -22903,7 +22899,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="4">
-        <f>'Chess Clock Grader #1'!C28</f>
+        <f>'Chess Clock Grader #2'!C28</f>
         <v>1</v>
       </c>
       <c r="E28" s="26"/>
@@ -22922,16 +22918,16 @@
         <v>1</v>
       </c>
       <c r="D29" s="4">
-        <f>'Chess Clock Grader #1'!C29</f>
+        <f>'Chess Clock Grader #2'!C29</f>
         <v>1</v>
       </c>
       <c r="E29" s="26"/>
-      <c r="F29" s="60" t="s">
+      <c r="F29" s="62" t="s">
         <v>96</v>
       </c>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
+      <c r="G29" s="63"/>
+      <c r="H29" s="63"/>
+      <c r="I29" s="63"/>
     </row>
     <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="str">
@@ -22947,8 +22943,8 @@
         <v>1</v>
       </c>
       <c r="D30" s="4">
-        <f>'Chess Clock Grader #1'!C30</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C30</f>
+        <v>0</v>
       </c>
       <c r="E30" s="26"/>
       <c r="F30" s="11" t="s">
@@ -23016,7 +23012,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="4">
-        <f>'Chess Clock Grader #1'!C31</f>
+        <f>'Chess Clock Grader #2'!C31</f>
         <v>1</v>
       </c>
       <c r="E31" s="26"/>
@@ -23061,7 +23057,7 @@
       </c>
       <c r="R31" s="39">
         <f t="shared" ref="R31:T31" si="42">($J31/$J$34) * (G$34/$J$34)</f>
-        <v>4.0000000000000008E-2</v>
+        <v>0.12</v>
       </c>
       <c r="S31" s="40">
         <f t="shared" si="42"/>
@@ -23069,7 +23065,7 @@
       </c>
       <c r="T31" s="41">
         <f t="shared" si="42"/>
-        <v>0.16000000000000003</v>
+        <v>8.0000000000000016E-2</v>
       </c>
       <c r="U31" s="11"/>
       <c r="V31" s="42" t="s">
@@ -23077,7 +23073,7 @@
       </c>
       <c r="W31" s="39">
         <f>SUMPRODUCT(G31:I33, M31:O33) /$J$34</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="X31" s="41" t="s">
         <v>106</v>
@@ -23097,7 +23093,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="4">
-        <f>'Chess Clock Grader #1'!C32</f>
+        <f>'Chess Clock Grader #2'!C32</f>
         <v>1</v>
       </c>
       <c r="E32" s="26"/>
@@ -23158,7 +23154,7 @@
       </c>
       <c r="W32" s="43">
         <f>SUMPRODUCT(R31:T33, M31:O33)</f>
-        <v>0.32000000000000006</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="X32" s="44" t="s">
         <v>108</v>
@@ -23178,8 +23174,8 @@
         <v>0.5</v>
       </c>
       <c r="D33" s="4">
-        <f>'Chess Clock Grader #1'!C33</f>
-        <v>0.5</v>
+        <f>'Chess Clock Grader #2'!C33</f>
+        <v>1</v>
       </c>
       <c r="E33" s="26"/>
       <c r="F33" s="38">
@@ -23187,7 +23183,7 @@
       </c>
       <c r="G33" s="45">
         <f>COUNTIFS($A$2:$A$46,$F$30,$C$2:$C$46,$F33,$D$2:$D$46,G$30) + MAX(C49-D49,0)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H33" s="46">
         <f>COUNTIFS($A$2:$A$90,$F$30,$C$2:$C$90,$F33,$D$2:$D$90,H$30)</f>
@@ -23195,7 +23191,7 @@
       </c>
       <c r="I33" s="47">
         <f>COUNTIFS($A$2:$A$46,$F$30,$C$2:$C$46,$F33,$D$2:$D$46,I$30) + MIN(C49,D49)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J33" s="11">
         <f t="shared" si="40"/>
@@ -23223,7 +23219,7 @@
       </c>
       <c r="R33" s="45">
         <f t="shared" ref="R33:T33" si="47">($J33/$J$34) * (G$34/$J$34)</f>
-        <v>0.16000000000000003</v>
+        <v>0.48</v>
       </c>
       <c r="S33" s="46">
         <f t="shared" si="47"/>
@@ -23231,7 +23227,7 @@
       </c>
       <c r="T33" s="47">
         <f t="shared" si="47"/>
-        <v>0.64000000000000012</v>
+        <v>0.32000000000000006</v>
       </c>
       <c r="U33" s="11"/>
       <c r="V33" s="42" t="s">
@@ -23239,7 +23235,7 @@
       </c>
       <c r="W33" s="45">
         <f>1-W31/W32</f>
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="X33" s="47" t="s">
         <v>109</v>
@@ -23259,7 +23255,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="4">
-        <f>'Chess Clock Grader #1'!C34</f>
+        <f>'Chess Clock Grader #2'!C34</f>
         <v>1</v>
       </c>
       <c r="E34" s="26"/>
@@ -23268,7 +23264,7 @@
       </c>
       <c r="G34" s="11">
         <f t="shared" ref="G34:I34" si="48">SUM(G31:G33)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H34" s="11">
         <f t="shared" si="48"/>
@@ -23276,7 +23272,7 @@
       </c>
       <c r="I34" s="11">
         <f t="shared" si="48"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J34" s="11">
         <f>SUM(G31:I33)</f>
@@ -23297,7 +23293,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="4">
-        <f>'Chess Clock Grader #1'!C35</f>
+        <f>'Chess Clock Grader #2'!C35</f>
         <v>1</v>
       </c>
       <c r="E35" s="26"/>
@@ -23316,16 +23312,16 @@
         <v>1</v>
       </c>
       <c r="D36" s="4">
-        <f>'Chess Clock Grader #1'!C36</f>
-        <v>1</v>
+        <f>'Chess Clock Grader #2'!C36</f>
+        <v>0</v>
       </c>
       <c r="E36" s="26"/>
-      <c r="F36" s="60" t="s">
+      <c r="F36" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
+      <c r="G36" s="63"/>
+      <c r="H36" s="63"/>
+      <c r="I36" s="63"/>
     </row>
     <row r="37" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="str">
@@ -23341,7 +23337,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="4">
-        <f>'Chess Clock Grader #1'!C37</f>
+        <f>'Chess Clock Grader #2'!C37</f>
         <v>1</v>
       </c>
       <c r="E37" s="26"/>
@@ -23410,7 +23406,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="4">
-        <f>'Chess Clock Grader #1'!C38</f>
+        <f>'Chess Clock Grader #2'!C38</f>
         <v>1</v>
       </c>
       <c r="E38" s="26"/>
@@ -23471,7 +23467,7 @@
       </c>
       <c r="W38" s="39">
         <f>SUMPRODUCT(G38:I40, M38:O40) /$J$41</f>
-        <v>0</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="X38" s="41" t="s">
         <v>106</v>
@@ -23491,7 +23487,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="4">
-        <f>'Chess Clock Grader #1'!C39</f>
+        <f>'Chess Clock Grader #2'!C39</f>
         <v>1</v>
       </c>
       <c r="E39" s="26"/>
@@ -23572,7 +23568,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="4">
-        <f>'Chess Clock Grader #1'!C40</f>
+        <f>'Chess Clock Grader #2'!C40</f>
         <v>1</v>
       </c>
       <c r="E40" s="26"/>
@@ -23585,11 +23581,11 @@
       </c>
       <c r="H40" s="46">
         <f>COUNTIFS($A$2:$A$90,$F$37,$C$2:$C$90,$F40,$D$2:$D$90,H$37)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" s="47">
         <f>COUNTIFS($A$2:$A$46,$F$37,$C$2:$C$46,$F40,$D$2:$D$46,I$37) + MIN(C50,D50)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J40" s="11">
         <f t="shared" si="50"/>
@@ -23653,7 +23649,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="4">
-        <f>'Chess Clock Grader #1'!C41</f>
+        <f>'Chess Clock Grader #2'!C41</f>
         <v>1</v>
       </c>
       <c r="E41" s="26"/>
@@ -23666,11 +23662,11 @@
       </c>
       <c r="H41" s="11">
         <f t="shared" si="58"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I41" s="11">
         <f t="shared" si="58"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J41" s="11">
         <f>SUM(G38:I40)</f>
@@ -23691,7 +23687,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="4">
-        <f>'Chess Clock Grader #1'!C42</f>
+        <f>'Chess Clock Grader #2'!C42</f>
         <v>1</v>
       </c>
       <c r="E42" s="26"/>
@@ -23710,16 +23706,16 @@
         <v>1</v>
       </c>
       <c r="D43" s="4">
-        <f>'Chess Clock Grader #1'!C43</f>
+        <f>'Chess Clock Grader #2'!C43</f>
         <v>1</v>
       </c>
       <c r="E43" s="26"/>
-      <c r="F43" s="60" t="s">
+      <c r="F43" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
+      <c r="G43" s="63"/>
+      <c r="H43" s="63"/>
+      <c r="I43" s="63"/>
     </row>
     <row r="44" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="str">
@@ -23735,7 +23731,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="4">
-        <f>'Chess Clock Grader #1'!C44</f>
+        <f>'Chess Clock Grader #2'!C44</f>
         <v>1</v>
       </c>
       <c r="E44" s="26"/>
@@ -23804,7 +23800,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="4">
-        <f>'Chess Clock Grader #1'!C45</f>
+        <f>'Chess Clock Grader #2'!C45</f>
         <v>1</v>
       </c>
       <c r="E45" s="26"/>
@@ -23884,8 +23880,8 @@
         <f>'Chess Clock Grader #1'!C46</f>
         <v>1</v>
       </c>
-      <c r="D46" s="54">
-        <f>'Chess Clock Grader #1'!C46</f>
+      <c r="D46" s="64">
+        <f>'Chess Clock Grader #2'!C46</f>
         <v>1</v>
       </c>
       <c r="E46" s="26"/>
@@ -23961,12 +23957,12 @@
         <f>'Chess Clock Grader #1'!B47</f>
         <v>additional elements</v>
       </c>
-      <c r="C47" s="55">
+      <c r="C47" s="54">
         <f>'Chess Clock Grader #1'!C47</f>
         <v>0</v>
       </c>
-      <c r="D47" s="56">
-        <f>'Chess Clock Grader #1'!C47</f>
+      <c r="D47" s="4">
+        <f>'Chess Clock Grader #2'!C47</f>
         <v>0</v>
       </c>
       <c r="E47" s="26"/>
@@ -24046,9 +24042,9 @@
         <f>'Chess Clock Grader #1'!C48</f>
         <v>1</v>
       </c>
-      <c r="D48" s="57">
-        <f>'Chess Clock Grader #1'!C48</f>
-        <v>1</v>
+      <c r="D48" s="4">
+        <f>'Chess Clock Grader #2'!C48</f>
+        <v>0</v>
       </c>
       <c r="E48" s="26"/>
       <c r="F48" s="48" t="s">
@@ -24084,8 +24080,8 @@
         <f>'Chess Clock Grader #1'!C49</f>
         <v>0</v>
       </c>
-      <c r="D49" s="57">
-        <f>'Chess Clock Grader #1'!C49</f>
+      <c r="D49" s="4">
+        <f>'Chess Clock Grader #2'!C49</f>
         <v>0</v>
       </c>
       <c r="E49" s="26"/>
@@ -24103,17 +24099,17 @@
         <f>'Chess Clock Grader #1'!C50</f>
         <v>0</v>
       </c>
-      <c r="D50" s="57">
-        <f>'Chess Clock Grader #1'!C50</f>
+      <c r="D50" s="4">
+        <f>'Chess Clock Grader #2'!C50</f>
         <v>0</v>
       </c>
       <c r="E50" s="26"/>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61"/>
+      <c r="G50" s="63"/>
+      <c r="H50" s="63"/>
+      <c r="I50" s="63"/>
     </row>
     <row r="51" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="str">
@@ -24128,8 +24124,8 @@
         <f>'Chess Clock Grader #1'!C51</f>
         <v>0</v>
       </c>
-      <c r="D51" s="57">
-        <f>'Chess Clock Grader #1'!C51</f>
+      <c r="D51" s="4">
+        <f>'Chess Clock Grader #2'!C51</f>
         <v>0</v>
       </c>
       <c r="E51" s="26"/>
@@ -24197,8 +24193,8 @@
         <f>'Chess Clock Grader #1'!C52</f>
         <v>0</v>
       </c>
-      <c r="D52" s="57">
-        <f>'Chess Clock Grader #1'!C52</f>
+      <c r="D52" s="4">
+        <f>'Chess Clock Grader #2'!C52</f>
         <v>0</v>
       </c>
       <c r="E52" s="26"/>
@@ -24247,11 +24243,11 @@
       </c>
       <c r="S52" s="40">
         <f t="shared" si="72"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="T52" s="41">
         <f t="shared" si="72"/>
-        <v>0.1111111111111111</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U52" s="11"/>
       <c r="V52" s="42" t="s">
@@ -24259,7 +24255,7 @@
       </c>
       <c r="W52" s="39">
         <f>SUMPRODUCT(G52:I54, M52:O54) /$J$55</f>
-        <v>0</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="X52" s="41" t="s">
         <v>106</v>
@@ -24278,8 +24274,8 @@
         <f>'Chess Clock Grader #1'!C53</f>
         <v>0</v>
       </c>
-      <c r="D53" s="57">
-        <f>'Chess Clock Grader #1'!C53</f>
+      <c r="D53" s="4">
+        <f>'Chess Clock Grader #2'!C53</f>
         <v>0</v>
       </c>
       <c r="E53" s="26"/>
@@ -24292,11 +24288,11 @@
       </c>
       <c r="H53" s="11">
         <f t="shared" si="73"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="44">
         <f t="shared" si="73"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J53" s="11">
         <f t="shared" si="70"/>
@@ -24328,11 +24324,11 @@
       </c>
       <c r="S53" s="11">
         <f t="shared" si="75"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="T53" s="44">
         <f t="shared" si="75"/>
-        <v>0.1111111111111111</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U53" s="11"/>
       <c r="V53" s="42" t="s">
@@ -24340,7 +24336,7 @@
       </c>
       <c r="W53" s="43">
         <f>SUMPRODUCT(R52:T54, M52:O54)</f>
-        <v>0.44444444444444442</v>
+        <v>0.5</v>
       </c>
       <c r="X53" s="44" t="s">
         <v>108</v>
@@ -24397,11 +24393,11 @@
       </c>
       <c r="S54" s="46">
         <f t="shared" si="77"/>
-        <v>0.1111111111111111</v>
+        <v>0</v>
       </c>
       <c r="T54" s="47">
         <f t="shared" si="77"/>
-        <v>0.1111111111111111</v>
+        <v>0.22222222222222221</v>
       </c>
       <c r="U54" s="11"/>
       <c r="V54" s="42" t="s">
@@ -24409,7 +24405,7 @@
       </c>
       <c r="W54" s="45">
         <f>1-W52/W53</f>
-        <v>1</v>
+        <v>0.66666666666666674</v>
       </c>
       <c r="X54" s="47" t="s">
         <v>109</v>
@@ -24430,11 +24426,11 @@
       </c>
       <c r="H55" s="11">
         <f t="shared" si="78"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I55" s="11">
         <f t="shared" si="78"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J55" s="11">
         <f>SUM(G52:I54)</f>
